--- a/FAST_Questions.xlsx
+++ b/FAST_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HARI\ciATHENA_Backup\ciathena_autoamtion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83529126-5FDF-4B7F-9AFD-F3226CEDB1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AA00F2-3105-4475-8C8C-72F76FE3A4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B82579B-A560-4715-9590-6777EC92C5A5}"/>
   </bookViews>
@@ -38,1744 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
-    <t>Expected Backend Response</t>
-  </si>
-  <si>
     <t>expected_sql</t>
   </si>
   <si>
     <t>question</t>
-  </si>
-  <si>
-    <t>Which HCPs are disadvantaged in FAST Score but still high prescribers?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Give me US state wise distribution of Cardizor Trx? </t>
-  </si>
-  <si>
-    <t>When compared against traditional performance benchmarks, how does FAST uncover true positives and false positives?</t>
-  </si>
-  <si>
-    <t>scatter</t>
-  </si>
-  <si>
-    <t>WITH HCPPerformance AS ( SELECT
-  "HCP_ID",
-  "HCP_FAST_ACCESS_SCORE",
-  SUM(CASE WHEN "PRODUCT" = 'CARDIZOR' THEN "VOLUME" ELSE 0 END) AS "CardizorVolume",
-  SUM("VOLUME") AS "TotalMarketVolume"
-FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX'
-GROUP BY "HCP_ID", "HCP_FAST_ACCESS_SCORE" ) SELECT h."HCP_ID", h."HCP_FAST_ACCESS_SCORE", (h."CardizorVolume" * 100.0) / NULLIF(h."TotalMarketVolume", 0) AS "Cardizor_Market_Share_Percentage"
-FROM HCPPerformance h
-WHERE h."CardizorVolume" &gt; 0 AND h."TotalMarketVolume" &gt; 0
-ORDER BY h."HCP_FAST_ACCESS_SCORE" ASC, "Cardizor_Market_Share_Percentage" DESC
-LIMIT 10;</t>
-  </si>
-  <si>
-    <t>[
-    {
-        "question": {
-            "type": "human",
-            "content": "Which HCPs are disadvantaged in FAST Score but still high prescribers?"
-        },
-        "answer": {
-            "type": "ai",
-            "content": "HCPs with a FAST Access Score of 0.0 but high prescribing activity for Cardizor demonstrate strong brand loyalty and prescribing commitment despite significant access barriers. Notably, the top prescribers in this segment, such as HCPs with IDs 30783496 and 5055833, maintain market shares of 30.95% and 29.45%, respectively. These HCPs represent critical opportunities for access improvement strategies to sustain and amplify their prescribing behavior.",
-            "sql_query": "WITH HCPPerformance AS (\n    SELECT\n        \"HCP_ID\",\n        \"HCP_FAST_ACCESS_SCORE\",\n        SUM(CASE WHEN \"PRODUCT\" = 'CARDIZOR' THEN \"VOLUME\" ELSE 0 END) AS \"CardizorVolume\",\n        SUM(\"VOLUME\") AS \"TotalMarketVolume\"\n    FROM \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\n    WHERE \"METRIC\" = 'TRX'\n    GROUP BY \"HCP_ID\", \"HCP_FAST_ACCESS_SCORE\"\n)\nSELECT\n    h.\"HCP_ID\",\n    h.\"HCP_FAST_ACCESS_SCORE\",\n    (h.\"CardizorVolume\" * 100.0) / NULLIF(h.\"TotalMarketVolume\", 0) AS \"Cardizor_Market_Share_Percentage\"\nFROM HCPPerformance h\nWHERE\n    h.\"CardizorVolume\" &gt; 0\n    AND h.\"TotalMarketVolume\" &gt; 0\nORDER BY\n    h.\"HCP_FAST_ACCESS_SCORE\" ASC,\n    \"Cardizor_Market_Share_Percentage\" DESC\nLIMIT 10;",
-            "sql_result": {
-                "datasets": [
-                    {
-                        "label": "Cardizor Market Share Percentage",
-                        "data": [
-                            {
-                                "x": 0,
-                                "y": 30.952380952380953,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 29.44564274255817,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 27.84504523683016,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 23.940206157965196,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 23.008861633651247,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 22.73482130430144,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 6.8780294280615895,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 6.25,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 4.074210973107712,
-                                "label": "",
-                                "category": "All"
-                            },
-                            {
-                                "x": 0,
-                                "y": 3.703703703703704,
-                                "label": "",
-                                "category": "All"
-                            }
-                        ],
-                        "type": "scatter",
-                        "format": "number"
-                    }
-                ]
-            },
-            "raw_sql_result": [
-                [
-                    "30783496",
-                    0,
-                    30.952380952380953
-                ],
-                [
-                    "5055833",
-                    0,
-                    29.445642742558174
-                ],
-                [
-                    "55040631",
-                    0,
-                    27.845045236830163
-                ],
-                [
-                    "28889698",
-                    0,
-                    23.940206157965193
-                ],
-                [
-                    "6929561",
-                    0,
-                    23.00886163365125
-                ],
-                [
-                    "36505827",
-                    0,
-                    22.73482130430144
-                ],
-                [
-                    "16416480",
-                    0,
-                    6.8780294280615895
-                ],
-                [
-                    "4744226",
-                    0,
-                    6.25
-                ],
-                [
-                    "35983642",
-                    0,
-                    4.0742109731077125
-                ],
-                [
-                    "6001760",
-                    0,
-                    3.7037037037037037
-                ]
-            ],
-            "result_headers": [
-                "Hcp Id",
-                "Hcp Fast Access Score",
-                "Cardizor Market Share Percentage"
-            ],
-            "visualization": "scatter",
-            "hypotheses": null,
-            "gathered_evidence": null,
-            "visualizations": null,
-            "x_label": "HCP Fast Access Score",
-            "y_label": "Cardizor Market Share Percentage",
-            "table_name": "Updated_FAST_Table_MVP_Unpivot",
-            "sql_query_summary": "- Retrieved HCPs with a FAST Access Score of 0.0 who have prescribed Cardizor.\n- Calculated the market share percentage of Cardizor for each HCP.\n- Limited results to the top 10 HCPs based on their market share percentage.",
-            "error": null,
-            "is_bookmarked": false,
-            "bookmark_id": null,
-            "user_vote": null,
-            "structured_allocation": null,
-            "structured_kpis": null,
-            "projected_kpis": null,
-            "scenario_name": null,
-            "total_budget": null,
-            "user_constraints": null,
-            "current_step": null,
-            "last_agent_prompt": null,
-            "suggestions": null,
-            "user_comment": null,
-            "is_regenerated_response": null,
-            "original_query_text": null,
-            "user_feedback_on_previous": null,
-            "structured_visualization_for_BS": null,
-            "analytical_table": null,
-            "newly_created_dashboard": null,
-            "category": [
-                "fast"
-            ],
-            "structured_table_data": null,
-            "structured_chart_data": null,
-            "simulation_input_data": null,
-            "ui_mode": null,
-            "dropdown_options": null,
-            "thinking_process": [
-                {
-                    "agent_title": "Intent Agent",
-                    "step_name": "intent_detection",
-                    "thought_content": "Analyzing your query: 'Which HCPs are disadvantaged in FAST Score but still high prescribers?' to determine the best analytical approach...",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Memory Agent",
-                    "step_name": "memory_scan",
-                    "thought_content": "Scanning the semantic cache to identify prior analyses related to FAST Score and high prescriber metrics, focusing on columns like HCP ID, FAST Score, and TRx volume. Reviewing timestamps and verification tags to ensure relevance and accuracy for the current query.",
-                    "status": "in_progress"
-                },
-                {
-                    "agent_title": "Routing Agent",
-                    "step_name": "router",
-                    "thought_content": "Reviewing the request to identify HCPs with low FAST Scores and high prescription volumes by focusing on the relevant metrics: FAST Score and TRx. Clarifying if the analysis should cover a specific timeframe or the most recent data available.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "generate_sql",
-                    "thought_content": "Identifying the relevant columns, such as HCP ID, FAST Score, and TRx, to structure the query for filtering high prescribers with low FAST Scores. Outlining the logic to compare FAST Score thresholds against TRx volumes for the specified cohort.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "validate_sql",
-                    "thought_content": "Validating the WHERE clause to ensure it correctly identifies HCPs with low FAST Scores and high prescription volumes using the FAST_Score and TRx columns. Confirming the JOIN conditions between the HCP table and prescription data are accurate to avoid mismatched records.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "execute_sql",
-                    "thought_content": "Running a query on the HCP_Prescriptions table to retrieve columns for HCP_ID, FAST_Score, and Total_Prescriptions. Filtering the data to include only HCPs with a FAST_Score below the threshold and high Total_Prescriptions.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Insights Agent",
-                    "step_name": "final_report",
-                    "thought_content": "Filtering the dataset to identify HCPs with low FAST Scores and high prescription volumes (TRx) over the past 12 months. Adding a column to flag these HCPs for easier segmentation in the final output.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Visualization Agent",
-                    "step_name": "visualization",
-                    "thought_content": "Filtering the dataset to identify HCPs with low FAST Scores and high prescription volumes using the columns 'FAST Score' and 'TRx'. Selecting a scatter plot to clearly display the relationship between these two metrics and highlight outliers.",
-                    "status": "success"
-                }
-            ],
-            "valid_charts": [
-                {
-                    "chart_type": "bubble",
-                    "data": {
-                        "datasets": [
-                            {
-                                "label": "Cardizor Market Share Percentage",
-                                "data": [
-                                    {
-                                        "x": 0,
-                                        "y": 30.952380952380953,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 29.44564274255817,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 27.84504523683016,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 23.940206157965196,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 23.008861633651247,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 22.73482130430144,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 6.8780294280615895,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 6.25,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 4.074210973107712,
-                                        "label": "",
-                                        "category": "All"
-                                    },
-                                    {
-                                        "x": 0,
-                                        "y": 3.703703703703704,
-                                        "label": "",
-                                        "category": "All"
-                                    }
-                                ],
-                                "type": "scatter",
-                                "format": "number"
-                            }
-                        ]
-                    }
-                }
-            ],
-            "title": "Cardizor Market Share Percentage by HCP Fast Access Score"
-        }
-    }
-]</t>
-  </si>
-  <si>
-    <t>SELECT
-  "STATE",
-  SUM("VOLUME") AS "CardizorTRXVolume"
-FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX' AND "PRODUCT" = 'CARDIZOR'
-GROUP BY "STATE"
-ORDER BY "CardizorTRXVolume" DESC;</t>
-  </si>
-  <si>
-    <t>[
-    {
-        "question": {
-            "type": "human",
-            "content": "Give me US state wise distribution of Cardizor Trx?"
-        },
-        "answer": {
-            "type": "ai",
-            "content": "Cardizor TRx volumes are highest in Texas, reaching 7,821.85, followed by New York with 5,114.84 and California at 3,662.05. Florida and Illinois also show significant activity with 3,538.98 and 3,336.31 TRx, respectively. States like New Mexico, Alaska, and Montana report the lowest TRx volumes, all under 125.",
-            "sql_query": "SELECT\n    \"STATE\",\n    SUM(\"VOLUME\") AS \"CardizorTRXVolume\"\nFROM\n    \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\nWHERE\n    \"METRIC\" = 'TRX'\n    AND \"PRODUCT\" = 'CARDIZOR'\nGROUP BY\n    \"STATE\"\nORDER BY\n    \"CardizorTRXVolume\" DESC;",
-            "sql_result": {
-                "data": [
-                    {
-                        "State": "AK",
-                        "Cardizor Trxvolume": 113.711117
-                    },
-                    {
-                        "State": "AL",
-                        "Cardizor Trxvolume": 2491.316337769
-                    },
-                    {
-                        "State": "AR",
-                        "Cardizor Trxvolume": 546.798292418
-                    },
-                    {
-                        "State": "AZ",
-                        "Cardizor Trxvolume": 668.771455569
-                    },
-                    {
-                        "State": "CA",
-                        "Cardizor Trxvolume": 3662.054841816
-                    },
-                    {
-                        "State": "CO",
-                        "Cardizor Trxvolume": 266.358984784
-                    },
-                    {
-                        "State": "CT",
-                        "Cardizor Trxvolume": 587.671587832
-                    },
-                    {
-                        "State": "DC",
-                        "Cardizor Trxvolume": 63.327049807
-                    },
-                    {
-                        "State": "DE",
-                        "Cardizor Trxvolume": 228.248408
-                    },
-                    {
-                        "State": "FL",
-                        "Cardizor Trxvolume": 3538.978133143
-                    },
-                    {
-                        "State": "GA",
-                        "Cardizor Trxvolume": 2740.507303626
-                    },
-                    {
-                        "State": "HI",
-                        "Cardizor Trxvolume": 119.932064
-                    },
-                    {
-                        "State": "IA",
-                        "Cardizor Trxvolume": 265.252668
-                    },
-                    {
-                        "State": "ID",
-                        "Cardizor Trxvolume": 187.037115
-                    },
-                    {
-                        "State": "IL",
-                        "Cardizor Trxvolume": 3336.313189279
-                    },
-                    {
-                        "State": "IN",
-                        "Cardizor Trxvolume": 2626.220820738
-                    },
-                    {
-                        "State": "KS",
-                        "Cardizor Trxvolume": 642.470686829
-                    },
-                    {
-                        "State": "KY",
-                        "Cardizor Trxvolume": 1001.197682474
-                    },
-                    {
-                        "State": "LA",
-                        "Cardizor Trxvolume": 1478.466746899
-                    },
-                    {
-                        "State": "MA",
-                        "Cardizor Trxvolume": 1403.811878486
-                    },
-                    {
-                        "State": "MD",
-                        "Cardizor Trxvolume": 1421.075954309
-                    },
-                    {
-                        "State": "ME",
-                        "Cardizor Trxvolume": 390.77107942
-                    },
-                    {
-                        "State": "MI",
-                        "Cardizor Trxvolume": 2552.352995594
-                    },
-                    {
-                        "State": "MN",
-                        "Cardizor Trxvolume": 1138.029162863
-                    },
-                    {
-                        "State": "MO",
-                        "Cardizor Trxvolume": 1898.082741189
-                    },
-                    {
-                        "State": "MS",
-                        "Cardizor Trxvolume": 570.559282879
-                    },
-                    {
-                        "State": "MT",
-                        "Cardizor Trxvolume": 122.653572
-                    },
-                    {
-                        "State": "NC",
-                        "Cardizor Trxvolume": 2829.569651522
-                    },
-                    {
-                        "State": "ND",
-                        "Cardizor Trxvolume": 454.740931
-                    },
-                    {
-                        "State": "NE",
-                        "Cardizor Trxvolume": 603.399071
-                    },
-                    {
-                        "State": "NH",
-                        "Cardizor Trxvolume": 373.650029219
-                    },
-                    {
-                        "State": "NJ",
-                        "Cardizor Trxvolume": 1980.274201473
-                    },
-                    {
-                        "State": "NM",
-                        "Cardizor Trxvolume": 63.966668
-                    },
-                    {
-                        "State": "NV",
-                        "Cardizor Trxvolume": 511.023507472
-                    },
-                    {
-                        "State": "NY",
-                        "Cardizor Trxvolume": 5114.843010983
-                    },
-                    {
-                        "State": "OH",
-                        "Cardizor Trxvolume": 3044.778736552
-                    },
-                    {
-                        "State": "OK",
-                        "Cardizor Trxvolume": 940.280559415
-                    },
-                    {
-                        "State": "OR",
-                        "Cardizor Trxvolume": 434.861296
-                    },
-                    {
-                        "State": "PA",
-                        "Cardizor Trxvolume": 2599.055642435
-                    },
-                    {
-                        "State": "PR",
-                        "Cardizor Trxvolume": 210.79612
-                    },
-                    {
-                        "State": "RI",
-                        "Cardizor Trxvolume": 445.088665971
-                    },
-                    {
-                        "State": "SC",
-                        "Cardizor Trxvolume": 1029.807946185
-                    },
-                    {
-                        "State": "SD",
-                        "Cardizor Trxvolume": 293.258242
-                    },
-                    {
-                        "State": "TN",
-                        "Cardizor Trxvolume": 2211.519125191
-                    },
-                    {
-                        "State": "TX",
-                        "Cardizor Trxvolume": 7821.84509114
-                    },
-                    {
-                        "State": "UT",
-                        "Cardizor Trxvolume": 138.273220195
-                    },
-                    {
-                        "State": "Unknown",
-                        "Cardizor Trxvolume": 114
-                    },
-                    {
-                        "State": "VA",
-                        "Cardizor Trxvolume": 1040.27672116
-                    },
-                    {
-                        "State": "VT",
-                        "Cardizor Trxvolume": 17
-                    },
-                    {
-                        "State": "WA",
-                        "Cardizor Trxvolume": 1811.492590726
-                    },
-                    {
-                        "State": "WI",
-                        "Cardizor Trxvolume": 983.066044581
-                    },
-                    {
-                        "State": "WV",
-                        "Cardizor Trxvolume": 342.792427029
-                    }
-                ]
-            },
-            "raw_sql_result": [
-                [
-                    "TX",
-                    7821.84509114
-                ],
-                [
-                    "NY",
-                    5114.843010983
-                ],
-                [
-                    "CA",
-                    3662.054841816
-                ],
-                [
-                    "FL",
-                    3538.978133143
-                ],
-                [
-                    "IL",
-                    3336.313189279
-                ],
-                [
-                    "OH",
-                    3044.778736552
-                ],
-                [
-                    "NC",
-                    2829.569651522
-                ],
-                [
-                    "GA",
-                    2740.507303626
-                ],
-                [
-                    "IN",
-                    2626.220820738
-                ],
-                [
-                    "PA",
-                    2599.055642435
-                ],
-                [
-                    "MI",
-                    2552.352995594
-                ],
-                [
-                    "AL",
-                    2491.316337769
-                ],
-                [
-                    "TN",
-                    2211.519125191
-                ],
-                [
-                    "NJ",
-                    1980.274201473
-                ],
-                [
-                    "MO",
-                    1898.082741189
-                ],
-                [
-                    "WA",
-                    1811.492590726
-                ],
-                [
-                    "LA",
-                    1478.466746899
-                ],
-                [
-                    "MD",
-                    1421.075954309
-                ],
-                [
-                    "MA",
-                    1403.811878486
-                ],
-                [
-                    "MN",
-                    1138.029162863
-                ],
-                [
-                    "VA",
-                    1040.27672116
-                ],
-                [
-                    "SC",
-                    1029.807946185
-                ],
-                [
-                    "KY",
-                    1001.197682474
-                ],
-                [
-                    "WI",
-                    983.066044581
-                ],
-                [
-                    "OK",
-                    940.280559415
-                ],
-                [
-                    "AZ",
-                    668.771455569
-                ],
-                [
-                    "KS",
-                    642.470686829
-                ],
-                [
-                    "NE",
-                    603.399071
-                ],
-                [
-                    "CT",
-                    587.671587832
-                ],
-                [
-                    "MS",
-                    570.559282879
-                ],
-                [
-                    "AR",
-                    546.798292418
-                ],
-                [
-                    "NV",
-                    511.023507472
-                ],
-                [
-                    "ND",
-                    454.740931
-                ],
-                [
-                    "RI",
-                    445.088665971
-                ],
-                [
-                    "OR",
-                    434.861296
-                ],
-                [
-                    "ME",
-                    390.77107942
-                ],
-                [
-                    "NH",
-                    373.650029219
-                ],
-                [
-                    "WV",
-                    342.792427029
-                ],
-                [
-                    "SD",
-                    293.258242
-                ],
-                [
-                    "CO",
-                    266.358984784
-                ],
-                [
-                    "IA",
-                    265.252668
-                ],
-                [
-                    "DE",
-                    228.248408
-                ],
-                [
-                    "PR",
-                    210.79612
-                ],
-                [
-                    "ID",
-                    187.037115
-                ],
-                [
-                    "UT",
-                    138.273220195
-                ],
-                [
-                    "MT",
-                    122.653572
-                ],
-                [
-                    "HI",
-                    119.932064
-                ],
-                [
-                    "Unknown",
-                    114
-                ],
-                [
-                    "AK",
-                    113.711117
-                ],
-                [
-                    "NM",
-                    63.966668
-                ],
-                [
-                    "DC",
-                    63.327049807
-                ],
-                [
-                    "VT",
-                    17
-                ]
-            ],
-            "result_headers": [
-                "State",
-                "Cardizor Trxvolume"
-            ],
-            "visualization": "us_heatmap",
-            "hypotheses": null,
-            "gathered_evidence": null,
-            "visualizations": null,
-            "x_label": "State",
-            "y_label": "Cardizor Trxvolume",
-            "table_name": "Updated_FAST_Table_MVP_Unpivot",
-            "sql_query_summary": "• Retrieved the total transaction volume of Cardizor by US state. • Filtered results for the metric 'TRX' and product 'CARDIZOR'. • Grouped the results by state and ordered them by transaction volume in descending order.",
-            "error": null,
-            "is_bookmarked": false,
-            "bookmark_id": null,
-            "user_vote": null,
-            "structured_allocation": null,
-            "structured_kpis": null,
-            "projected_kpis": null,
-            "scenario_name": null,
-            "total_budget": null,
-            "user_constraints": null,
-            "current_step": null,
-            "last_agent_prompt": null,
-            "suggestions": null,
-            "user_comment": null,
-            "is_regenerated_response": null,
-            "original_query_text": null,
-            "user_feedback_on_previous": null,
-            "structured_visualization_for_BS": null,
-            "analytical_table": null,
-            "newly_created_dashboard": null,
-            "category": [
-                "fast"
-            ],
-            "structured_table_data": null,
-            "structured_chart_data": null,
-            "simulation_input_data": null,
-            "ui_mode": null,
-            "dropdown_options": null,
-            "thinking_process": [
-                {
-                    "agent_title": "Intent Agent",
-                    "step_name": "intent_detection",
-                    "thought_content": "Analyzing your query: 'Give me US state wise distribution of Cardizor Trx?' to determine the best analytical approach...",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Memory Agent",
-                    "step_name": "memory_scan",
-                    "thought_content": "Scanning the semantic cache to identify prior solutions related to US state-wise distribution of Cardizor TRx. Reviewing stored queries and verified outputs to determine if this specific analysis has already been addressed.",
-                    "status": "in_progress"
-                },
-                {
-                    "agent_title": "Routing Agent",
-                    "step_name": "router",
-                    "thought_content": "Clarifying the request by confirming that \"Cardizor Trx\" refers to transaction counts and identifying if a specific timeframe is required for the US state-wise distribution.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "generate_sql",
-                    "thought_content": "Structuring the SQL query to select the \"state\" column for geographic segmentation and \"Cardizor Trx\" as the metric. Adding filters to ensure the data is specific to the United States.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "validate_sql",
-                    "thought_content": "Reviewing the SQL query to confirm the \"US State\" column is correctly joined with the \"Cardizor Trx\" data. Verifying the filter logic ensures only valid transactions are included without duplicates.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Data Operations Agent",
-                    "step_name": "execute_sql",
-                    "thought_content": "Running a SQL query on the transactions table to retrieve the total TRx for Cardizor, grouped by US state. Filtering the dataset to include only relevant columns: state, product name, and TRx count.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Insights Agent",
-                    "step_name": "final_report",
-                    "thought_content": "Formatting the state-wise distribution of Cardizor TRx into a clear table, ensuring the column for states aligns with the TRx metric. Adding a recommendation to visualize this data using a heatmap for better geographical insights.",
-                    "status": "success"
-                },
-                {
-                    "agent_title": "Visualization Agent",
-                    "step_name": "visualization",
-                    "thought_content": "Filtering the dataset to extract TRx values for Cardizor grouped by US states. Designing a choropleth map to visually represent the distribution across states for clearer geographic insights.",
-                    "status": "success"
-                }
-            ],
-            "valid_charts": [
-                {
-                    "chart_type": "column",
-                    "data": {
-                        "data": [
-                            [
-                                "TX",
-                                7821.84509114
-                            ],
-                            [
-                                "NY",
-                                5114.843010983
-                            ],
-                            [
-                                "CA",
-                                3662.054841816
-                            ],
-                            [
-                                "FL",
-                                3538.978133143
-                            ],
-                            [
-                                "IL",
-                                3336.313189279
-                            ],
-                            [
-                                "OH",
-                                3044.778736552
-                            ],
-                            [
-                                "NC",
-                                2829.569651522
-                            ],
-                            [
-                                "GA",
-                                2740.507303626
-                            ],
-                            [
-                                "IN",
-                                2626.220820738
-                            ],
-                            [
-                                "PA",
-                                2599.055642435
-                            ],
-                            [
-                                "MI",
-                                2552.352995594
-                            ],
-                            [
-                                "AL",
-                                2491.316337769
-                            ],
-                            [
-                                "TN",
-                                2211.519125191
-                            ],
-                            [
-                                "NJ",
-                                1980.274201473
-                            ],
-                            [
-                                "MO",
-                                1898.082741189
-                            ],
-                            [
-                                "WA",
-                                1811.492590726
-                            ],
-                            [
-                                "LA",
-                                1478.466746899
-                            ],
-                            [
-                                "MD",
-                                1421.075954309
-                            ],
-                            [
-                                "MA",
-                                1403.811878486
-                            ],
-                            [
-                                "MN",
-                                1138.029162863
-                            ],
-                            [
-                                "VA",
-                                1040.27672116
-                            ],
-                            [
-                                "SC",
-                                1029.807946185
-                            ],
-                            [
-                                "KY",
-                                1001.197682474
-                            ],
-                            [
-                                "WI",
-                                983.066044581
-                            ],
-                            [
-                                "OK",
-                                940.280559415
-                            ],
-                            [
-                                "AZ",
-                                668.771455569
-                            ],
-                            [
-                                "KS",
-                                642.470686829
-                            ],
-                            [
-                                "NE",
-                                603.399071
-                            ],
-                            [
-                                "CT",
-                                587.671587832
-                            ],
-                            [
-                                "MS",
-                                570.559282879
-                            ],
-                            [
-                                "AR",
-                                546.798292418
-                            ],
-                            [
-                                "NV",
-                                511.023507472
-                            ],
-                            [
-                                "ND",
-                                454.740931
-                            ],
-                            [
-                                "RI",
-                                445.088665971
-                            ],
-                            [
-                                "OR",
-                                434.861296
-                            ],
-                            [
-                                "ME",
-                                390.77107942
-                            ],
-                            [
-                                "NH",
-                                373.650029219
-                            ],
-                            [
-                                "WV",
-                                342.792427029
-                            ],
-                            [
-                                "SD",
-                                293.258242
-                            ],
-                            [
-                                "CO",
-                                266.358984784
-                            ],
-                            [
-                                "IA",
-                                265.252668
-                            ],
-                            [
-                                "DE",
-                                228.248408
-                            ],
-                            [
-                                "PR",
-                                210.79612
-                            ],
-                            [
-                                "ID",
-                                187.037115
-                            ],
-                            [
-                                "UT",
-                                138.273220195
-                            ],
-                            [
-                                "MT",
-                                122.653572
-                            ],
-                            [
-                                "HI",
-                                119.932064
-                            ],
-                            [
-                                "Unknown",
-                                114
-                            ],
-                            [
-                                "AK",
-                                113.711117
-                            ],
-                            [
-                                "NM",
-                                63.966668
-                            ],
-                            [
-                                "DC",
-                                63.327049807
-                            ],
-                            [
-                                "VT",
-                                17
-                            ]
-                        ],
-                        "format": "number"
-                    }
-                }
-            ],
-            "title": "Cardizor Trxvolume by State"
-        }
-    }
-]</t>
-  </si>
-  <si>
-    <t>us_heatmap</t>
-  </si>
-  <si>
-    <t>WITH period_cast AS ( SELECT
-  "HCP_ID",
-  "PAYER_NAME",
-  "PAYER_ID",
-  "PERIOD",
-  "TIER",
-  "PAYMENT_CHANNEL",
-  "INDICATION",
-  "METRIC",
-  "CARDIZOR_SHARE",
-  "FAST_ACCESS_SCORE",
-  "FAST_SCORE_CATEGORY",
-  "SPECIALTY",
-  "STATE",
-  "REGION",
-  "AREA",
-  "TERRITORY",
-  "CARDIZOR_VOLUME_DECILE",
-  "MARKET_VOLUME_DECILE",
-  "CARDIZOR_VOLUME_DECILE_BUCKET",
-  "MARKET_VOLUME_DECILE_BUCKET",
-  "CURRENT_FUTURE_FLAG",
-  "EVENT_FLAG",
-  "CARDIZOR_PREVIOUS_ACCESS",
-  "CHANGE_TYPE",
-  "RELATIVE_CARDIZOR_VS_COMPETITOR2_ACCESS",
-  "RELATIVE_CARDIZOR_VS_COMPETITOR1_ACCESS",
-  "RELATIVE_CARDIZOR_VS_COMPETITOR3_ACCESS",
-  "CARDIZOR_ACCESS_FLAG",
-  "LIVES",
-  "PBM_NAME",
-  "PRODUCT",
-  "VOLUME",
-  "ACCESS",
-  "BENCHMARK_SHARE",
-  "BENCHMARK_FAST_SCORE",
-  "PERFORMANCE_CATEGORY",
-  "FAST_BENCHMARK_SHARE",
-  "FAST_PERFORMANCE_INDICATOR",
-  "MARKET_VOLUME",
-  "INCREMENTAL_TRX_OPPORTUNITY",
-  "FAST_INCREMENTAL_MARKET_SHARE_OPPORTUNITY",
-  "TRADITIONAL_BENCHMARK_SHARE",
-  "TRADITIONAL_FAST_PERFORMANCE_INDICATOR",
-  "TRADITIONAL_INCREMENTAL_TRX_OPPORTUNITY",
-  "TRADITIONAL_INCREMENTAL_MARKET_SHARE_OPPORTUNITY",
-  "CARDIZOR_ACCESS_FAVORABILITY",
-  "COMPETITOR1_ACCESS_FAVORABILITY",
-  "COMPETITOR2_ACCESS_FAVORABILITY",
-  "COMPETITOR3_ACCESS_FAVORABILITY",
-  "FAST_ACCESS_SCORE_BUCKET",
-  "HCP_PAYER_FAST_ACCESS_SCORE",
-  "HCP_FAST_ACCESS_SCORE",
-  "PAYER_FAST_ACCESS_SCORE",
-  "STATE_FAST_ACCESS_SCORE",
-  "TRADITIONAL_SCORE",
-  CASE WHEN "PERIOD" ~ '^[0-9]{6}"fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
-FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
-FROM period_cast u CROSS
-JOIN LATEST_PERIOD_CTE l
-WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
-GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
-HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
-FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
-FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
-FROM SCORED_HCP_CATEGORIES
-WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
-ORDER BY scaled_fast_access_score DESC; THEN to_date("PERIOD",'YYYYMM') WHEN "PERIOD" ~ '^[0-9]{4}-[0-9]{2}-[0-9]{2}"fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
-FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
-FROM period_cast u CROSS
-JOIN LATEST_PERIOD_CTE l
-WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
-GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
-HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
-FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
-FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
-FROM SCORED_HCP_CATEGORIES
-WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
-ORDER BY scaled_fast_access_score DESC; THEN to_date("PERIOD",'YYYY-MM-DD') ELSE NULL END AS period_date
-FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
-FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
-FROM period_cast u CROSS
-JOIN LATEST_PERIOD_CTE l
-WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
-GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
-HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
-FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
-FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
-FROM SCORED_HCP_CATEGORIES
-WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
-ORDER BY scaled_fast_access_score DESC;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[
-    {
-        "question": {
-            "type": "human",
-            "content": "When compared against traditional performance benchmarks, how does FAST uncover true positives and false positives?"
-        },
-        "answer": {
-            "type": "ai",
-            "content": "FAST uncovers true positives more effectively than traditional benchmarks by isolating HCPs with high access-driven growth potential. Traditional benchmarks often misclassify HCPs as high performers based on historical volume, overlooking their limited access scalability. FAST re-ranks these HCPs, ensuring focus on those with both high TRx share and favorable access scores. This reduces false positives and aligns resources toward HCPs with the greatest incremental opportunity, optimizing commercial impact.",
-            "sql_query": "WITH period_cast AS (\n    SELECT\n        \"HCP_ID\",\n        \"PAYER_NAME\",\n        \"PAYER_ID\",\n        \"PERIOD\",\n        \"TIER\",\n        \"PAYMENT_CHANNEL\",\n        \"INDICATION\",\n        \"METRIC\",\n        \"CARDIZOR_SHARE\",\n        \"FAST_ACCESS_SCORE\",\n        \"FAST_SCORE_CATEGORY\",\n        \"SPECIALTY\",\n        \"STATE\",\n        \"REGION\",\n        \"AREA\",\n        \"TERRITORY\",\n        \"CARDIZOR_VOLUME_DECILE\",\n        \"MARKET_VOLUME_DECILE\",\n        \"CARDIZOR_VOLUME_DECILE_BUCKET\",\n        \"MARKET_VOLUME_DECILE_BUCKET\",\n        \"CURRENT_FUTURE_FLAG\",\n        \"EVENT_FLAG\",\n        \"CARDIZOR_PREVIOUS_ACCESS\",\n        \"CHANGE_TYPE\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR2_ACCESS\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR1_ACCESS\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR3_ACCESS\",\n        \"CARDIZOR_ACCESS_FLAG\",\n        \"LIVES\",\n        \"PBM_NAME\",\n        \"PRODUCT\",\n        \"VOLUME\",\n        \"ACCESS\",\n        \"BENCHMARK_SHARE\",\n        \"BENCHMARK_FAST_SCORE\",\n        \"PERFORMANCE_CATEGORY\",\n        \"FAST_BENCHMARK_SHARE\",\n        \"FAST_PERFORMANCE_INDICATOR\",\n        \"MARKET_VOLUME\",\n        \"INCREMENTAL_TRX_OPPORTUNITY\",\n        \"FAST_INCREMENTAL_MARKET_SHARE_OPPORTUNITY\",\n        \"TRADITIONAL_BENCHMARK_SHARE\",\n        \"TRADITIONAL_FAST_PERFORMANCE_INDICATOR\",\n        \"TRADITIONAL_INCREMENTAL_TRX_OPPORTUNITY\",\n        \"TRADITIONAL_INCREMENTAL_MARKET_SHARE_OPPORTUNITY\",\n        \"CARDIZOR_ACCESS_FAVORABILITY\",\n        \"COMPETITOR1_ACCESS_FAVORABILITY\",\n        \"COMPETITOR2_ACCESS_FAVORABILITY\",\n        \"COMPETITOR3_ACCESS_FAVORABILITY\",\n        \"FAST_ACCESS_SCORE_BUCKET\",\n        \"HCP_PAYER_FAST_ACCESS_SCORE\",\n        \"HCP_FAST_ACCESS_SCORE\",\n        \"PAYER_FAST_ACCESS_SCORE\",\n        \"STATE_FAST_ACCESS_SCORE\",\n        \"TRADITIONAL_SCORE\",\n        CASE\n            WHEN \"PERIOD\" ~ '^[0-9]{6}$' THEN to_date(\"PERIOD\",'YYYYMM')\n            WHEN \"PERIOD\" ~ '^[0-9]{4}-[0-9]{2}-[0-9]{2}$' THEN to_date(\"PERIOD\",'YYYY-MM-DD')\n            ELSE NULL\n        END AS period_date\n    FROM \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\n    WHERE \"METRIC\" = 'TRX'\n),\n\nLATEST_PERIOD_CTE AS (\n    SELECT MAX(period_date) AS latest_period\n    FROM period_cast\n),\n\nHCP_FAST_SCORES AS (\n    SELECT\n        u.\"HCP_ID\",\n        u.\"BENCHMARK_FAST_SCORE\",\n        AVG(u.\"TRADITIONAL_SCORE\") AS benchmark_traditional_fast_score,\n\n        SUM(\n            CASE WHEN u.period_date = l.latest_period\n                 THEN u.\"VOLUME\" * u.\"FAST_ACCESS_SCORE\"\n                 ELSE 0\n            END\n        ) / NULLIF(SUM(u.\"VOLUME\"),0) AS fast_access_score,\n\n        SUM(\n            CASE WHEN u.period_date = l.latest_period\n                 THEN u.\"VOLUME\" * u.\"TRADITIONAL_SCORE\"\n                 ELSE 0\n            END\n        ) / NULLIF(SUM(u.\"VOLUME\"),0) AS traditional_access_score,\n\n        SUM(CASE WHEN UPPER(u.\"PRODUCT\")='CARDIZOR'\n                 THEN u.\"VOLUME\" ELSE 0 END)\n        / NULLIF(SUM(u.\"VOLUME\"),0) AS market_share\n\n    FROM period_cast u\n    CROSS JOIN LATEST_PERIOD_CTE l\n\n    WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'\n\n    GROUP BY u.\"HCP_ID\", u.\"BENCHMARK_FAST_SCORE\"\n\n    HAVING SUM(CASE WHEN UPPER(u.\"PRODUCT\")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0\n),\n\nSCALED_HCP_SCORES AS (\n    SELECT\n        \"HCP_ID\",\n        fast_access_score,\n        traditional_access_score,\n        \"BENCHMARK_FAST_SCORE\",\n        benchmark_traditional_fast_score,\n        market_share,\n\n        CASE\n            WHEN fast_access_score IS NULL\n                 OR NULLIF(MAX(fast_access_score) OVER()\n                            - MIN(fast_access_score) OVER(),0) IS NULL\n            THEN NULL\n            ELSE (fast_access_score - MIN(fast_access_score) OVER())\n                / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER())\n        END AS scaled_fast_access_score,\n\n        CASE\n            WHEN traditional_access_score IS NULL\n                 OR NULLIF(MAX(traditional_access_score) OVER()\n                            - MIN(traditional_access_score) OVER(),0) IS NULL\n            THEN NULL\n            ELSE (traditional_access_score - MIN(traditional_access_score) OVER())\n                / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER())\n        END AS scaled_traditional_access_score\n\n    FROM HCP_FAST_SCORES\n),\n\nSCORED_HCP_CATEGORIES AS (\n    SELECT\n        \"HCP_ID\",\n        scaled_fast_access_score,\n        scaled_traditional_access_score,\n        \"BENCHMARK_FAST_SCORE\",\n        benchmark_traditional_fast_score,\n        market_share\n    FROM SCALED_HCP_SCORES\n)\n\nSELECT\n    \"HCP_ID\",\n    \"BENCHMARK_FAST_SCORE\",\n    market_share AS CardizorMarketShare,\n    scaled_fast_access_score AS ScaledFastAccessScore,\n    scaled_traditional_access_score AS ScaledTraditionalAccessScore,\n    CASE\n        WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n         AND scaled_fast_access_score &gt; \"BENCHMARK_FAST_SCORE\"\n        THEN 'True Positive (Traditional)'\n        WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n         AND scaled_fast_access_score &lt; \"BENCHMARK_FAST_SCORE\"\n        THEN 'False Positive (Traditional)'\n        ELSE NULL\n    END AS performance_category\n\nFROM SCORED_HCP_CATEGORIES\n\nWHERE (\n        CASE\n            WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n             AND scaled_fast_access_score &gt; \"BENCHMARK_FAST_SCORE\"\n            THEN 'True Positive (Traditional)'\n            WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n             AND scaled_fast_access_score &lt; \"BENCHMARK_FAST_SCORE\"\n            THEN 'False Positive (Traditional)'\n            ELSE NULL\n        END\n    ) IS NOT NULL\n\nORDER BY scaled_fast_access_score DESC;",
-            "sql_result": {
-                "datasets": [
-                    {
-                        "label": "False Positive (Traditional)",
-                        "data": [
-                            {
-                                "x": 0,
-                                "y": 0.3874946440616334,
-                                "label": "18649543",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3935300471138515,
-                                "label": "6068217",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3915677510645455,
-                                "label": "25274950",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3914179863394806,
-                                "label": "5295748",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3893263407054183,
-                                "label": "10446538",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4025505204461489,
-                                "label": "4192409",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4019657649107294,
-                                "label": "3704415",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4017239993460303,
-                                "label": "5095785",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4082877163462044,
-                                "label": "5105268",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3842515018029714,
-                                "label": "5915529",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3842156366418556,
-                                "label": "30783585",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3125543801914136,
-                                "label": "22480976",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3259477346591404,
-                                "label": "35632174",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3258144357642281,
-                                "label": "7565912",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3232225022233223,
-                                "label": "5881491",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3188560435439515,
-                                "label": "6651599",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3173561188048308,
-                                "label": "12048657",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3541804187250981,
-                                "label": "19094039",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.339631682968026,
-                                "label": "51379424",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.304129220229656,
-                                "label": "6960359",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3088219184676404,
-                                "label": "4164810",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3339982205228334,
-                                "label": "53039620",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.2401264254135473,
-                                "label": "4503189",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3305058447742187,
-                                "label": "5292523",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3290235469634846,
-                                "label": "6726003",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3278500197829481,
-                                "label": "31464258",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3570227574353444,
-                                "label": "5531065",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.355622692772102,
-                                "label": "21744867",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3551975194353741,
-                                "label": "18639675",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4218726491362665,
-                                "label": "25133384",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3763773031701457,
-                                "label": "14498627",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.373932674330407,
-                                "label": "5276650",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3733232861279524,
-                                "label": "4204481",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3508618689311831,
-                                "label": "6099963",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3319860810385752,
-                                "label": "10555664",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3672761869425729,
-                                "label": "29550857",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4193764676047008,
-                                "label": "5365433",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4191454092576291,
-                                "label": "21211686",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4175708556941284,
-                                "label": "11200242",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4174156640824562,
-                                "label": "36683939",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4164620224574064,
-                                "label": "16446680",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3721038034708753,
-                                "label": "5558018",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3705974206423312,
-                                "label": "15645592",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.3704080444471938,
-                                "label": "30776906",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4116921747376069,
-                                "label": "3524687",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4205587642498535,
-                                "label": "22449641",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0,
-                                "y": 0.4204414884220036,
-                                "label": "5502540",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.004582774455002714,
-                                "y": 0.3558601415685602,
-                                "label": "19675949",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.0046576988835141655,
-                                "y": 0.3688230571664206,
-                                "label": "36546418",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.005837857771131241,
-                                "y": 0.3680883111437548,
-                                "label": "6102534",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.0062709444344555935,
-                                "y": 0.3805927295303305,
-                                "label": "5196023",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.007401824859096735,
-                                "y": 0.3010710171047162,
-                                "label": "21008142",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.008084066354762056,
-                                "y": 0.3320686542818434,
-                                "label": "21022057",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.008881894604053454,
-                                "y": 0.3902520009569326,
-                                "label": "19109317",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.008968291752521245,
-                                "y": 0.3947005446878356,
-                                "label": "36704585",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.009185977522742859,
-                                "y": 0.2761697379823667,
-                                "label": "5867307",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.01198077911888755,
-                                "y": 0.410963032837742,
-                                "label": "4210101",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.013259668449681024,
-                                "y": 0.3535216710107509,
-                                "label": "11652342",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.01369138373770162,
-                                "y": 0.3396532328920984,
-                                "label": "5773469",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.01380362021588821,
-                                "y": 0.3791109741281477,
-                                "label": "36225737",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.01470202134268915,
-                                "y": 0.3471037993287987,
-                                "label": "4327705",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.015335984658038046,
-                                "y": 0.3552242930684143,
-                                "label": "36510261",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.015469690942815542,
-                                "y": 0.3914587115115856,
-                                "label": "7758079",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.016293905918419622,
-                                "y": 0.2995747892453196,
-                                "label": "36701578",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.02120725038523451,
-                                "y": 0.4148970781644029,
-                                "label": "5476675",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.02366244896784663,
-                                "y": 0.366271235342624,
-                                "label": "24645458",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.024152763183889942,
-                                "y": 0.3652129074449832,
-                                "label": "5992603",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.0243288484578676,
-                                "y": 0.2824266981329426,
-                                "label": "30819826",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.026102005593288055,
-                                "y": 0.4158716685673361,
-                                "label": "21388776",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.026143790849673203,
-                                "y": 0.3813313743015811,
-                                "label": "19517810",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.026296893565883377,
-                                "y": 0.2631735228501205,
-                                "label": "27290224",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.027522935779816515,
-                                "y": 0.4011575373663379,
-                                "label": "5502837",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.029289775766301245,
-                                "y": 0.3629546263628366,
-                                "label": "17637050",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.02972865768219462,
-                                "y": 0.4111477468213231,
-                                "label": "4232085",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.029888642952339683,
-                                "y": 0.2667912174486982,
-                                "label": "4542753",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.030687135535582517,
-                                "y": 0.2985331227811728,
-                                "label": "4449247",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03136678336105225,
-                                "y": 0.3869786789357152,
-                                "label": "21155831",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.0345051026437382,
-                                "y": 0.3144732216484961,
-                                "label": "36594149",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03557661393522737,
-                                "y": 0.3608480150871822,
-                                "label": "6790997",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.036036834530030024,
-                                "y": 0.292709245981445,
-                                "label": "8292486",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03650297842098907,
-                                "y": 0.3806356466732214,
-                                "label": "6153731",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03677542234209638,
-                                "y": 0.4060404666087371,
-                                "label": "39518335",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03744849133515562,
-                                "y": 0.3762530105162919,
-                                "label": "6929326",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03785520478667046,
-                                "y": 0.2703158592770471,
-                                "label": "19260606",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.038710240915647176,
-                                "y": 0.411569385092177,
-                                "label": "36703130",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.03944254556635575,
-                                "y": 0.2912098678588501,
-                                "label": "4670935",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.040021011991799985,
-                                "y": 0.2237108317020096,
-                                "label": "18348520",
-                                "category": "False Positive (Traditional)"
-                            },
-                            {
-                                "x": 0.040931174632194166,
-                         </t>
-  </si>
-  <si>
-    <t>benchmark_cluster</t>
   </si>
   <si>
     <t>chart</t>
@@ -5004,6 +3270,9 @@
 ]</t>
   </si>
   <si>
+    <t>final_response_json</t>
+  </si>
+  <si>
     <t>Which HCP cohorts present incremental opportunity potential in the Market or the Brand, and Access Favorability?</t>
   </si>
   <si>
@@ -5921,6 +4190,1737 @@
         }
     }
 ]</t>
+  </si>
+  <si>
+    <t>scatter</t>
+  </si>
+  <si>
+    <t>Which HCPs are disadvantaged in FAST Score but still high prescribers?</t>
+  </si>
+  <si>
+    <t>WITH HCPPerformance AS ( SELECT
+  "HCP_ID",
+  "HCP_FAST_ACCESS_SCORE",
+  SUM(CASE WHEN "PRODUCT" = 'CARDIZOR' THEN "VOLUME" ELSE 0 END) AS "CardizorVolume",
+  SUM("VOLUME") AS "TotalMarketVolume"
+FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX'
+GROUP BY "HCP_ID", "HCP_FAST_ACCESS_SCORE" ) SELECT h."HCP_ID", h."HCP_FAST_ACCESS_SCORE", (h."CardizorVolume" * 100.0) / NULLIF(h."TotalMarketVolume", 0) AS "Cardizor_Market_Share_Percentage"
+FROM HCPPerformance h
+WHERE h."CardizorVolume" &gt; 0 AND h."TotalMarketVolume" &gt; 0
+ORDER BY h."HCP_FAST_ACCESS_SCORE" ASC, "Cardizor_Market_Share_Percentage" DESC
+LIMIT 10;</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "question": {
+            "type": "human",
+            "content": "Which HCPs are disadvantaged in FAST Score but still high prescribers?"
+        },
+        "answer": {
+            "type": "ai",
+            "content": "HCPs with a FAST Access Score of 0.0 but high prescribing activity for Cardizor demonstrate strong brand loyalty and prescribing commitment despite significant access barriers. Notably, the top prescribers in this segment, such as HCPs with IDs 30783496 and 5055833, maintain market shares of 30.95% and 29.45%, respectively. These HCPs represent critical opportunities for access improvement strategies to sustain and amplify their prescribing behavior.",
+            "sql_query": "WITH HCPPerformance AS (\n    SELECT\n        \"HCP_ID\",\n        \"HCP_FAST_ACCESS_SCORE\",\n        SUM(CASE WHEN \"PRODUCT\" = 'CARDIZOR' THEN \"VOLUME\" ELSE 0 END) AS \"CardizorVolume\",\n        SUM(\"VOLUME\") AS \"TotalMarketVolume\"\n    FROM \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\n    WHERE \"METRIC\" = 'TRX'\n    GROUP BY \"HCP_ID\", \"HCP_FAST_ACCESS_SCORE\"\n)\nSELECT\n    h.\"HCP_ID\",\n    h.\"HCP_FAST_ACCESS_SCORE\",\n    (h.\"CardizorVolume\" * 100.0) / NULLIF(h.\"TotalMarketVolume\", 0) AS \"Cardizor_Market_Share_Percentage\"\nFROM HCPPerformance h\nWHERE\n    h.\"CardizorVolume\" &gt; 0\n    AND h.\"TotalMarketVolume\" &gt; 0\nORDER BY\n    h.\"HCP_FAST_ACCESS_SCORE\" ASC,\n    \"Cardizor_Market_Share_Percentage\" DESC\nLIMIT 10;",
+            "sql_result": {
+                "datasets": [
+                    {
+                        "label": "Cardizor Market Share Percentage",
+                        "data": [
+                            {
+                                "x": 0,
+                                "y": 30.952380952380953,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 29.44564274255817,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 27.84504523683016,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 23.940206157965196,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 23.008861633651247,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 22.73482130430144,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 6.8780294280615895,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 6.25,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 4.074210973107712,
+                                "label": "",
+                                "category": "All"
+                            },
+                            {
+                                "x": 0,
+                                "y": 3.703703703703704,
+                                "label": "",
+                                "category": "All"
+                            }
+                        ],
+                        "type": "scatter",
+                        "format": "number"
+                    }
+                ]
+            },
+            "raw_sql_result": [
+                [
+                    "30783496",
+                    0,
+                    30.952380952380953
+                ],
+                [
+                    "5055833",
+                    0,
+                    29.445642742558174
+                ],
+                [
+                    "55040631",
+                    0,
+                    27.845045236830163
+                ],
+                [
+                    "28889698",
+                    0,
+                    23.940206157965193
+                ],
+                [
+                    "6929561",
+                    0,
+                    23.00886163365125
+                ],
+                [
+                    "36505827",
+                    0,
+                    22.73482130430144
+                ],
+                [
+                    "16416480",
+                    0,
+                    6.8780294280615895
+                ],
+                [
+                    "4744226",
+                    0,
+                    6.25
+                ],
+                [
+                    "35983642",
+                    0,
+                    4.0742109731077125
+                ],
+                [
+                    "6001760",
+                    0,
+                    3.7037037037037037
+                ]
+            ],
+            "result_headers": [
+                "Hcp Id",
+                "Hcp Fast Access Score",
+                "Cardizor Market Share Percentage"
+            ],
+            "visualization": "scatter",
+            "hypotheses": null,
+            "gathered_evidence": null,
+            "visualizations": null,
+            "x_label": "HCP Fast Access Score",
+            "y_label": "Cardizor Market Share Percentage",
+            "table_name": "Updated_FAST_Table_MVP_Unpivot",
+            "sql_query_summary": "- Retrieved HCPs with a FAST Access Score of 0.0 who have prescribed Cardizor.\n- Calculated the market share percentage of Cardizor for each HCP.\n- Limited results to the top 10 HCPs based on their market share percentage.",
+            "error": null,
+            "is_bookmarked": false,
+            "bookmark_id": null,
+            "user_vote": null,
+            "structured_allocation": null,
+            "structured_kpis": null,
+            "projected_kpis": null,
+            "scenario_name": null,
+            "total_budget": null,
+            "user_constraints": null,
+            "current_step": null,
+            "last_agent_prompt": null,
+            "suggestions": null,
+            "user_comment": null,
+            "is_regenerated_response": null,
+            "original_query_text": null,
+            "user_feedback_on_previous": null,
+            "structured_visualization_for_BS": null,
+            "analytical_table": null,
+            "newly_created_dashboard": null,
+            "category": [
+                "fast"
+            ],
+            "structured_table_data": null,
+            "structured_chart_data": null,
+            "simulation_input_data": null,
+            "ui_mode": null,
+            "dropdown_options": null,
+            "thinking_process": [
+                {
+                    "agent_title": "Intent Agent",
+                    "step_name": "intent_detection",
+                    "thought_content": "Analyzing your query: 'Which HCPs are disadvantaged in FAST Score but still high prescribers?' to determine the best analytical approach...",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Memory Agent",
+                    "step_name": "memory_scan",
+                    "thought_content": "Scanning the semantic cache to identify prior analyses related to FAST Score and high prescriber metrics, focusing on columns like HCP ID, FAST Score, and TRx volume. Reviewing timestamps and verification tags to ensure relevance and accuracy for the current query.",
+                    "status": "in_progress"
+                },
+                {
+                    "agent_title": "Routing Agent",
+                    "step_name": "router",
+                    "thought_content": "Reviewing the request to identify HCPs with low FAST Scores and high prescription volumes by focusing on the relevant metrics: FAST Score and TRx. Clarifying if the analysis should cover a specific timeframe or the most recent data available.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "generate_sql",
+                    "thought_content": "Identifying the relevant columns, such as HCP ID, FAST Score, and TRx, to structure the query for filtering high prescribers with low FAST Scores. Outlining the logic to compare FAST Score thresholds against TRx volumes for the specified cohort.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "validate_sql",
+                    "thought_content": "Validating the WHERE clause to ensure it correctly identifies HCPs with low FAST Scores and high prescription volumes using the FAST_Score and TRx columns. Confirming the JOIN conditions between the HCP table and prescription data are accurate to avoid mismatched records.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "execute_sql",
+                    "thought_content": "Running a query on the HCP_Prescriptions table to retrieve columns for HCP_ID, FAST_Score, and Total_Prescriptions. Filtering the data to include only HCPs with a FAST_Score below the threshold and high Total_Prescriptions.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Insights Agent",
+                    "step_name": "final_report",
+                    "thought_content": "Filtering the dataset to identify HCPs with low FAST Scores and high prescription volumes (TRx) over the past 12 months. Adding a column to flag these HCPs for easier segmentation in the final output.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Visualization Agent",
+                    "step_name": "visualization",
+                    "thought_content": "Filtering the dataset to identify HCPs with low FAST Scores and high prescription volumes using the columns 'FAST Score' and 'TRx'. Selecting a scatter plot to clearly display the relationship between these two metrics and highlight outliers.",
+                    "status": "success"
+                }
+            ],
+            "valid_charts": [
+                {
+                    "chart_type": "bubble",
+                    "data": {
+                        "datasets": [
+                            {
+                                "label": "Cardizor Market Share Percentage",
+                                "data": [
+                                    {
+                                        "x": 0,
+                                        "y": 30.952380952380953,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 29.44564274255817,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 27.84504523683016,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 23.940206157965196,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 23.008861633651247,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 22.73482130430144,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 6.8780294280615895,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 6.25,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 4.074210973107712,
+                                        "label": "",
+                                        "category": "All"
+                                    },
+                                    {
+                                        "x": 0,
+                                        "y": 3.703703703703704,
+                                        "label": "",
+                                        "category": "All"
+                                    }
+                                ],
+                                "type": "scatter",
+                                "format": "number"
+                            }
+                        ]
+                    }
+                }
+            ],
+            "title": "Cardizor Market Share Percentage by HCP Fast Access Score"
+        }
+    }
+]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give me US state wise distribution of Cardizor Trx? </t>
+  </si>
+  <si>
+    <t>SELECT
+  "STATE",
+  SUM("VOLUME") AS "CardizorTRXVolume"
+FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX' AND "PRODUCT" = 'CARDIZOR'
+GROUP BY "STATE"
+ORDER BY "CardizorTRXVolume" DESC;</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "question": {
+            "type": "human",
+            "content": "Give me US state wise distribution of Cardizor Trx?"
+        },
+        "answer": {
+            "type": "ai",
+            "content": "Cardizor TRx volumes are highest in Texas, reaching 7,821.85, followed by New York with 5,114.84 and California at 3,662.05. Florida and Illinois also show significant activity with 3,538.98 and 3,336.31 TRx, respectively. States like New Mexico, Alaska, and Montana report the lowest TRx volumes, all under 125.",
+            "sql_query": "SELECT\n    \"STATE\",\n    SUM(\"VOLUME\") AS \"CardizorTRXVolume\"\nFROM\n    \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\nWHERE\n    \"METRIC\" = 'TRX'\n    AND \"PRODUCT\" = 'CARDIZOR'\nGROUP BY\n    \"STATE\"\nORDER BY\n    \"CardizorTRXVolume\" DESC;",
+            "sql_result": {
+                "data": [
+                    {
+                        "State": "AK",
+                        "Cardizor Trxvolume": 113.711117
+                    },
+                    {
+                        "State": "AL",
+                        "Cardizor Trxvolume": 2491.316337769
+                    },
+                    {
+                        "State": "AR",
+                        "Cardizor Trxvolume": 546.798292418
+                    },
+                    {
+                        "State": "AZ",
+                        "Cardizor Trxvolume": 668.771455569
+                    },
+                    {
+                        "State": "CA",
+                        "Cardizor Trxvolume": 3662.054841816
+                    },
+                    {
+                        "State": "CO",
+                        "Cardizor Trxvolume": 266.358984784
+                    },
+                    {
+                        "State": "CT",
+                        "Cardizor Trxvolume": 587.671587832
+                    },
+                    {
+                        "State": "DC",
+                        "Cardizor Trxvolume": 63.327049807
+                    },
+                    {
+                        "State": "DE",
+                        "Cardizor Trxvolume": 228.248408
+                    },
+                    {
+                        "State": "FL",
+                        "Cardizor Trxvolume": 3538.978133143
+                    },
+                    {
+                        "State": "GA",
+                        "Cardizor Trxvolume": 2740.507303626
+                    },
+                    {
+                        "State": "HI",
+                        "Cardizor Trxvolume": 119.932064
+                    },
+                    {
+                        "State": "IA",
+                        "Cardizor Trxvolume": 265.252668
+                    },
+                    {
+                        "State": "ID",
+                        "Cardizor Trxvolume": 187.037115
+                    },
+                    {
+                        "State": "IL",
+                        "Cardizor Trxvolume": 3336.313189279
+                    },
+                    {
+                        "State": "IN",
+                        "Cardizor Trxvolume": 2626.220820738
+                    },
+                    {
+                        "State": "KS",
+                        "Cardizor Trxvolume": 642.470686829
+                    },
+                    {
+                        "State": "KY",
+                        "Cardizor Trxvolume": 1001.197682474
+                    },
+                    {
+                        "State": "LA",
+                        "Cardizor Trxvolume": 1478.466746899
+                    },
+                    {
+                        "State": "MA",
+                        "Cardizor Trxvolume": 1403.811878486
+                    },
+                    {
+                        "State": "MD",
+                        "Cardizor Trxvolume": 1421.075954309
+                    },
+                    {
+                        "State": "ME",
+                        "Cardizor Trxvolume": 390.77107942
+                    },
+                    {
+                        "State": "MI",
+                        "Cardizor Trxvolume": 2552.352995594
+                    },
+                    {
+                        "State": "MN",
+                        "Cardizor Trxvolume": 1138.029162863
+                    },
+                    {
+                        "State": "MO",
+                        "Cardizor Trxvolume": 1898.082741189
+                    },
+                    {
+                        "State": "MS",
+                        "Cardizor Trxvolume": 570.559282879
+                    },
+                    {
+                        "State": "MT",
+                        "Cardizor Trxvolume": 122.653572
+                    },
+                    {
+                        "State": "NC",
+                        "Cardizor Trxvolume": 2829.569651522
+                    },
+                    {
+                        "State": "ND",
+                        "Cardizor Trxvolume": 454.740931
+                    },
+                    {
+                        "State": "NE",
+                        "Cardizor Trxvolume": 603.399071
+                    },
+                    {
+                        "State": "NH",
+                        "Cardizor Trxvolume": 373.650029219
+                    },
+                    {
+                        "State": "NJ",
+                        "Cardizor Trxvolume": 1980.274201473
+                    },
+                    {
+                        "State": "NM",
+                        "Cardizor Trxvolume": 63.966668
+                    },
+                    {
+                        "State": "NV",
+                        "Cardizor Trxvolume": 511.023507472
+                    },
+                    {
+                        "State": "NY",
+                        "Cardizor Trxvolume": 5114.843010983
+                    },
+                    {
+                        "State": "OH",
+                        "Cardizor Trxvolume": 3044.778736552
+                    },
+                    {
+                        "State": "OK",
+                        "Cardizor Trxvolume": 940.280559415
+                    },
+                    {
+                        "State": "OR",
+                        "Cardizor Trxvolume": 434.861296
+                    },
+                    {
+                        "State": "PA",
+                        "Cardizor Trxvolume": 2599.055642435
+                    },
+                    {
+                        "State": "PR",
+                        "Cardizor Trxvolume": 210.79612
+                    },
+                    {
+                        "State": "RI",
+                        "Cardizor Trxvolume": 445.088665971
+                    },
+                    {
+                        "State": "SC",
+                        "Cardizor Trxvolume": 1029.807946185
+                    },
+                    {
+                        "State": "SD",
+                        "Cardizor Trxvolume": 293.258242
+                    },
+                    {
+                        "State": "TN",
+                        "Cardizor Trxvolume": 2211.519125191
+                    },
+                    {
+                        "State": "TX",
+                        "Cardizor Trxvolume": 7821.84509114
+                    },
+                    {
+                        "State": "UT",
+                        "Cardizor Trxvolume": 138.273220195
+                    },
+                    {
+                        "State": "Unknown",
+                        "Cardizor Trxvolume": 114
+                    },
+                    {
+                        "State": "VA",
+                        "Cardizor Trxvolume": 1040.27672116
+                    },
+                    {
+                        "State": "VT",
+                        "Cardizor Trxvolume": 17
+                    },
+                    {
+                        "State": "WA",
+                        "Cardizor Trxvolume": 1811.492590726
+                    },
+                    {
+                        "State": "WI",
+                        "Cardizor Trxvolume": 983.066044581
+                    },
+                    {
+                        "State": "WV",
+                        "Cardizor Trxvolume": 342.792427029
+                    }
+                ]
+            },
+            "raw_sql_result": [
+                [
+                    "TX",
+                    7821.84509114
+                ],
+                [
+                    "NY",
+                    5114.843010983
+                ],
+                [
+                    "CA",
+                    3662.054841816
+                ],
+                [
+                    "FL",
+                    3538.978133143
+                ],
+                [
+                    "IL",
+                    3336.313189279
+                ],
+                [
+                    "OH",
+                    3044.778736552
+                ],
+                [
+                    "NC",
+                    2829.569651522
+                ],
+                [
+                    "GA",
+                    2740.507303626
+                ],
+                [
+                    "IN",
+                    2626.220820738
+                ],
+                [
+                    "PA",
+                    2599.055642435
+                ],
+                [
+                    "MI",
+                    2552.352995594
+                ],
+                [
+                    "AL",
+                    2491.316337769
+                ],
+                [
+                    "TN",
+                    2211.519125191
+                ],
+                [
+                    "NJ",
+                    1980.274201473
+                ],
+                [
+                    "MO",
+                    1898.082741189
+                ],
+                [
+                    "WA",
+                    1811.492590726
+                ],
+                [
+                    "LA",
+                    1478.466746899
+                ],
+                [
+                    "MD",
+                    1421.075954309
+                ],
+                [
+                    "MA",
+                    1403.811878486
+                ],
+                [
+                    "MN",
+                    1138.029162863
+                ],
+                [
+                    "VA",
+                    1040.27672116
+                ],
+                [
+                    "SC",
+                    1029.807946185
+                ],
+                [
+                    "KY",
+                    1001.197682474
+                ],
+                [
+                    "WI",
+                    983.066044581
+                ],
+                [
+                    "OK",
+                    940.280559415
+                ],
+                [
+                    "AZ",
+                    668.771455569
+                ],
+                [
+                    "KS",
+                    642.470686829
+                ],
+                [
+                    "NE",
+                    603.399071
+                ],
+                [
+                    "CT",
+                    587.671587832
+                ],
+                [
+                    "MS",
+                    570.559282879
+                ],
+                [
+                    "AR",
+                    546.798292418
+                ],
+                [
+                    "NV",
+                    511.023507472
+                ],
+                [
+                    "ND",
+                    454.740931
+                ],
+                [
+                    "RI",
+                    445.088665971
+                ],
+                [
+                    "OR",
+                    434.861296
+                ],
+                [
+                    "ME",
+                    390.77107942
+                ],
+                [
+                    "NH",
+                    373.650029219
+                ],
+                [
+                    "WV",
+                    342.792427029
+                ],
+                [
+                    "SD",
+                    293.258242
+                ],
+                [
+                    "CO",
+                    266.358984784
+                ],
+                [
+                    "IA",
+                    265.252668
+                ],
+                [
+                    "DE",
+                    228.248408
+                ],
+                [
+                    "PR",
+                    210.79612
+                ],
+                [
+                    "ID",
+                    187.037115
+                ],
+                [
+                    "UT",
+                    138.273220195
+                ],
+                [
+                    "MT",
+                    122.653572
+                ],
+                [
+                    "HI",
+                    119.932064
+                ],
+                [
+                    "Unknown",
+                    114
+                ],
+                [
+                    "AK",
+                    113.711117
+                ],
+                [
+                    "NM",
+                    63.966668
+                ],
+                [
+                    "DC",
+                    63.327049807
+                ],
+                [
+                    "VT",
+                    17
+                ]
+            ],
+            "result_headers": [
+                "State",
+                "Cardizor Trxvolume"
+            ],
+            "visualization": "us_heatmap",
+            "hypotheses": null,
+            "gathered_evidence": null,
+            "visualizations": null,
+            "x_label": "State",
+            "y_label": "Cardizor Trxvolume",
+            "table_name": "Updated_FAST_Table_MVP_Unpivot",
+            "sql_query_summary": "• Retrieved the total transaction volume of Cardizor by US state. • Filtered results for the metric 'TRX' and product 'CARDIZOR'. • Grouped the results by state and ordered them by transaction volume in descending order.",
+            "error": null,
+            "is_bookmarked": false,
+            "bookmark_id": null,
+            "user_vote": null,
+            "structured_allocation": null,
+            "structured_kpis": null,
+            "projected_kpis": null,
+            "scenario_name": null,
+            "total_budget": null,
+            "user_constraints": null,
+            "current_step": null,
+            "last_agent_prompt": null,
+            "suggestions": null,
+            "user_comment": null,
+            "is_regenerated_response": null,
+            "original_query_text": null,
+            "user_feedback_on_previous": null,
+            "structured_visualization_for_BS": null,
+            "analytical_table": null,
+            "newly_created_dashboard": null,
+            "category": [
+                "fast"
+            ],
+            "structured_table_data": null,
+            "structured_chart_data": null,
+            "simulation_input_data": null,
+            "ui_mode": null,
+            "dropdown_options": null,
+            "thinking_process": [
+                {
+                    "agent_title": "Intent Agent",
+                    "step_name": "intent_detection",
+                    "thought_content": "Analyzing your query: 'Give me US state wise distribution of Cardizor Trx?' to determine the best analytical approach...",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Memory Agent",
+                    "step_name": "memory_scan",
+                    "thought_content": "Scanning the semantic cache to identify prior solutions related to US state-wise distribution of Cardizor TRx. Reviewing stored queries and verified outputs to determine if this specific analysis has already been addressed.",
+                    "status": "in_progress"
+                },
+                {
+                    "agent_title": "Routing Agent",
+                    "step_name": "router",
+                    "thought_content": "Clarifying the request by confirming that \"Cardizor Trx\" refers to transaction counts and identifying if a specific timeframe is required for the US state-wise distribution.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "generate_sql",
+                    "thought_content": "Structuring the SQL query to select the \"state\" column for geographic segmentation and \"Cardizor Trx\" as the metric. Adding filters to ensure the data is specific to the United States.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "validate_sql",
+                    "thought_content": "Reviewing the SQL query to confirm the \"US State\" column is correctly joined with the \"Cardizor Trx\" data. Verifying the filter logic ensures only valid transactions are included without duplicates.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Data Operations Agent",
+                    "step_name": "execute_sql",
+                    "thought_content": "Running a SQL query on the transactions table to retrieve the total TRx for Cardizor, grouped by US state. Filtering the dataset to include only relevant columns: state, product name, and TRx count.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Insights Agent",
+                    "step_name": "final_report",
+                    "thought_content": "Formatting the state-wise distribution of Cardizor TRx into a clear table, ensuring the column for states aligns with the TRx metric. Adding a recommendation to visualize this data using a heatmap for better geographical insights.",
+                    "status": "success"
+                },
+                {
+                    "agent_title": "Visualization Agent",
+                    "step_name": "visualization",
+                    "thought_content": "Filtering the dataset to extract TRx values for Cardizor grouped by US states. Designing a choropleth map to visually represent the distribution across states for clearer geographic insights.",
+                    "status": "success"
+                }
+            ],
+            "valid_charts": [
+                {
+                    "chart_type": "column",
+                    "data": {
+                        "data": [
+                            [
+                                "TX",
+                                7821.84509114
+                            ],
+                            [
+                                "NY",
+                                5114.843010983
+                            ],
+                            [
+                                "CA",
+                                3662.054841816
+                            ],
+                            [
+                                "FL",
+                                3538.978133143
+                            ],
+                            [
+                                "IL",
+                                3336.313189279
+                            ],
+                            [
+                                "OH",
+                                3044.778736552
+                            ],
+                            [
+                                "NC",
+                                2829.569651522
+                            ],
+                            [
+                                "GA",
+                                2740.507303626
+                            ],
+                            [
+                                "IN",
+                                2626.220820738
+                            ],
+                            [
+                                "PA",
+                                2599.055642435
+                            ],
+                            [
+                                "MI",
+                                2552.352995594
+                            ],
+                            [
+                                "AL",
+                                2491.316337769
+                            ],
+                            [
+                                "TN",
+                                2211.519125191
+                            ],
+                            [
+                                "NJ",
+                                1980.274201473
+                            ],
+                            [
+                                "MO",
+                                1898.082741189
+                            ],
+                            [
+                                "WA",
+                                1811.492590726
+                            ],
+                            [
+                                "LA",
+                                1478.466746899
+                            ],
+                            [
+                                "MD",
+                                1421.075954309
+                            ],
+                            [
+                                "MA",
+                                1403.811878486
+                            ],
+                            [
+                                "MN",
+                                1138.029162863
+                            ],
+                            [
+                                "VA",
+                                1040.27672116
+                            ],
+                            [
+                                "SC",
+                                1029.807946185
+                            ],
+                            [
+                                "KY",
+                                1001.197682474
+                            ],
+                            [
+                                "WI",
+                                983.066044581
+                            ],
+                            [
+                                "OK",
+                                940.280559415
+                            ],
+                            [
+                                "AZ",
+                                668.771455569
+                            ],
+                            [
+                                "KS",
+                                642.470686829
+                            ],
+                            [
+                                "NE",
+                                603.399071
+                            ],
+                            [
+                                "CT",
+                                587.671587832
+                            ],
+                            [
+                                "MS",
+                                570.559282879
+                            ],
+                            [
+                                "AR",
+                                546.798292418
+                            ],
+                            [
+                                "NV",
+                                511.023507472
+                            ],
+                            [
+                                "ND",
+                                454.740931
+                            ],
+                            [
+                                "RI",
+                                445.088665971
+                            ],
+                            [
+                                "OR",
+                                434.861296
+                            ],
+                            [
+                                "ME",
+                                390.77107942
+                            ],
+                            [
+                                "NH",
+                                373.650029219
+                            ],
+                            [
+                                "WV",
+                                342.792427029
+                            ],
+                            [
+                                "SD",
+                                293.258242
+                            ],
+                            [
+                                "CO",
+                                266.358984784
+                            ],
+                            [
+                                "IA",
+                                265.252668
+                            ],
+                            [
+                                "DE",
+                                228.248408
+                            ],
+                            [
+                                "PR",
+                                210.79612
+                            ],
+                            [
+                                "ID",
+                                187.037115
+                            ],
+                            [
+                                "UT",
+                                138.273220195
+                            ],
+                            [
+                                "MT",
+                                122.653572
+                            ],
+                            [
+                                "HI",
+                                119.932064
+                            ],
+                            [
+                                "Unknown",
+                                114
+                            ],
+                            [
+                                "AK",
+                                113.711117
+                            ],
+                            [
+                                "NM",
+                                63.966668
+                            ],
+                            [
+                                "DC",
+                                63.327049807
+                            ],
+                            [
+                                "VT",
+                                17
+                            ]
+                        ],
+                        "format": "number"
+                    }
+                }
+            ],
+            "title": "Cardizor Trxvolume by State"
+        }
+    }
+]</t>
+  </si>
+  <si>
+    <t>us_heatmap</t>
+  </si>
+  <si>
+    <t>When compared against traditional performance benchmarks, how does FAST uncover true positives and false positives?</t>
+  </si>
+  <si>
+    <t>WITH period_cast AS ( SELECT
+  "HCP_ID",
+  "PAYER_NAME",
+  "PAYER_ID",
+  "PERIOD",
+  "TIER",
+  "PAYMENT_CHANNEL",
+  "INDICATION",
+  "METRIC",
+  "CARDIZOR_SHARE",
+  "FAST_ACCESS_SCORE",
+  "FAST_SCORE_CATEGORY",
+  "SPECIALTY",
+  "STATE",
+  "REGION",
+  "AREA",
+  "TERRITORY",
+  "CARDIZOR_VOLUME_DECILE",
+  "MARKET_VOLUME_DECILE",
+  "CARDIZOR_VOLUME_DECILE_BUCKET",
+  "MARKET_VOLUME_DECILE_BUCKET",
+  "CURRENT_FUTURE_FLAG",
+  "EVENT_FLAG",
+  "CARDIZOR_PREVIOUS_ACCESS",
+  "CHANGE_TYPE",
+  "RELATIVE_CARDIZOR_VS_COMPETITOR2_ACCESS",
+  "RELATIVE_CARDIZOR_VS_COMPETITOR1_ACCESS",
+  "RELATIVE_CARDIZOR_VS_COMPETITOR3_ACCESS",
+  "CARDIZOR_ACCESS_FLAG",
+  "LIVES",
+  "PBM_NAME",
+  "PRODUCT",
+  "VOLUME",
+  "ACCESS",
+  "BENCHMARK_SHARE",
+  "BENCHMARK_FAST_SCORE",
+  "PERFORMANCE_CATEGORY",
+  "FAST_BENCHMARK_SHARE",
+  "FAST_PERFORMANCE_INDICATOR",
+  "MARKET_VOLUME",
+  "INCREMENTAL_TRX_OPPORTUNITY",
+  "FAST_INCREMENTAL_MARKET_SHARE_OPPORTUNITY",
+  "TRADITIONAL_BENCHMARK_SHARE",
+  "TRADITIONAL_FAST_PERFORMANCE_INDICATOR",
+  "TRADITIONAL_INCREMENTAL_TRX_OPPORTUNITY",
+  "TRADITIONAL_INCREMENTAL_MARKET_SHARE_OPPORTUNITY",
+  "CARDIZOR_ACCESS_FAVORABILITY",
+  "COMPETITOR1_ACCESS_FAVORABILITY",
+  "COMPETITOR2_ACCESS_FAVORABILITY",
+  "COMPETITOR3_ACCESS_FAVORABILITY",
+  "FAST_ACCESS_SCORE_BUCKET",
+  "HCP_PAYER_FAST_ACCESS_SCORE",
+  "HCP_FAST_ACCESS_SCORE",
+  "PAYER_FAST_ACCESS_SCORE",
+  "STATE_FAST_ACCESS_SCORE",
+  "TRADITIONAL_SCORE",
+  CASE WHEN "PERIOD" ~ '^[0-9]{6}"fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
+FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
+FROM period_cast u CROSS
+JOIN LATEST_PERIOD_CTE l
+WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
+GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
+HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
+FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
+FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
+FROM SCORED_HCP_CATEGORIES
+WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
+ORDER BY scaled_fast_access_score DESC; THEN to_date("PERIOD",'YYYYMM') WHEN "PERIOD" ~ '^[0-9]{4}-[0-9]{2}-[0-9]{2}"fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
+FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
+FROM period_cast u CROSS
+JOIN LATEST_PERIOD_CTE l
+WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
+GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
+HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
+FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
+FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
+FROM SCORED_HCP_CATEGORIES
+WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
+ORDER BY scaled_fast_access_score DESC; THEN to_date("PERIOD",'YYYY-MM-DD') ELSE NULL END AS period_date
+FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX' ), LATEST_PERIOD_CTE AS ( SELECT MAX(period_date) AS latest_period
+FROM period_cast ), HCP_FAST_SCORES AS ( SELECT u."HCP_ID", u."BENCHMARK_FAST_SCORE", AVG(u."TRADITIONAL_SCORE") AS benchmark_traditional_fast_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."FAST_ACCESS_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS fast_access_score, SUM( CASE WHEN u.period_date = l.latest_period THEN u."VOLUME" * u."TRADITIONAL_SCORE" ELSE 0 END ) / NULLIF(SUM(u."VOLUME"),0) AS traditional_access_score, SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN u."VOLUME" ELSE 0 END) / NULLIF(SUM(u."VOLUME"),0) AS market_share
+FROM period_cast u CROSS
+JOIN LATEST_PERIOD_CTE l
+WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'
+GROUP BY u."HCP_ID", u."BENCHMARK_FAST_SCORE"
+HAVING SUM(CASE WHEN UPPER(u."PRODUCT")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0 ), SCALED_HCP_SCORES AS ( SELECT "HCP_ID", fast_access_score, traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share, CASE WHEN fast_access_score IS NULL OR NULLIF(MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER(),0) IS NULL THEN NULL ELSE (fast_access_score - MIN(fast_access_score) OVER()) / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER()) END AS scaled_fast_access_score, CASE WHEN traditional_access_score IS NULL OR NULLIF(MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER(),0) IS NULL THEN NULL ELSE (traditional_access_score - MIN(traditional_access_score) OVER()) / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER()) END AS scaled_traditional_access_score
+FROM HCP_FAST_SCORES ), SCORED_HCP_CATEGORIES AS ( SELECT "HCP_ID", scaled_fast_access_score, scaled_traditional_access_score, "BENCHMARK_FAST_SCORE", benchmark_traditional_fast_score, market_share
+FROM SCALED_HCP_SCORES ) SELECT "HCP_ID", "BENCHMARK_FAST_SCORE", market_share AS CardizorMarketShare, scaled_fast_access_score AS ScaledFastAccessScore, scaled_traditional_access_score AS ScaledTraditionalAccessScore, CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END AS performance_category
+FROM SCORED_HCP_CATEGORIES
+WHERE ( CASE WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &gt; "BENCHMARK_FAST_SCORE" THEN 'True Positive (Traditional)' WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score AND scaled_fast_access_score &lt; "BENCHMARK_FAST_SCORE" THEN 'False Positive (Traditional)' ELSE NULL END ) IS NOT NULL
+ORDER BY scaled_fast_access_score DESC;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[
+    {
+        "question": {
+            "type": "human",
+            "content": "When compared against traditional performance benchmarks, how does FAST uncover true positives and false positives?"
+        },
+        "answer": {
+            "type": "ai",
+            "content": "FAST uncovers true positives more effectively than traditional benchmarks by isolating HCPs with high access-driven growth potential. Traditional benchmarks often misclassify HCPs as high performers based on historical volume, overlooking their limited access scalability. FAST re-ranks these HCPs, ensuring focus on those with both high TRx share and favorable access scores. This reduces false positives and aligns resources toward HCPs with the greatest incremental opportunity, optimizing commercial impact.",
+            "sql_query": "WITH period_cast AS (\n    SELECT\n        \"HCP_ID\",\n        \"PAYER_NAME\",\n        \"PAYER_ID\",\n        \"PERIOD\",\n        \"TIER\",\n        \"PAYMENT_CHANNEL\",\n        \"INDICATION\",\n        \"METRIC\",\n        \"CARDIZOR_SHARE\",\n        \"FAST_ACCESS_SCORE\",\n        \"FAST_SCORE_CATEGORY\",\n        \"SPECIALTY\",\n        \"STATE\",\n        \"REGION\",\n        \"AREA\",\n        \"TERRITORY\",\n        \"CARDIZOR_VOLUME_DECILE\",\n        \"MARKET_VOLUME_DECILE\",\n        \"CARDIZOR_VOLUME_DECILE_BUCKET\",\n        \"MARKET_VOLUME_DECILE_BUCKET\",\n        \"CURRENT_FUTURE_FLAG\",\n        \"EVENT_FLAG\",\n        \"CARDIZOR_PREVIOUS_ACCESS\",\n        \"CHANGE_TYPE\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR2_ACCESS\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR1_ACCESS\",\n        \"RELATIVE_CARDIZOR_VS_COMPETITOR3_ACCESS\",\n        \"CARDIZOR_ACCESS_FLAG\",\n        \"LIVES\",\n        \"PBM_NAME\",\n        \"PRODUCT\",\n        \"VOLUME\",\n        \"ACCESS\",\n        \"BENCHMARK_SHARE\",\n        \"BENCHMARK_FAST_SCORE\",\n        \"PERFORMANCE_CATEGORY\",\n        \"FAST_BENCHMARK_SHARE\",\n        \"FAST_PERFORMANCE_INDICATOR\",\n        \"MARKET_VOLUME\",\n        \"INCREMENTAL_TRX_OPPORTUNITY\",\n        \"FAST_INCREMENTAL_MARKET_SHARE_OPPORTUNITY\",\n        \"TRADITIONAL_BENCHMARK_SHARE\",\n        \"TRADITIONAL_FAST_PERFORMANCE_INDICATOR\",\n        \"TRADITIONAL_INCREMENTAL_TRX_OPPORTUNITY\",\n        \"TRADITIONAL_INCREMENTAL_MARKET_SHARE_OPPORTUNITY\",\n        \"CARDIZOR_ACCESS_FAVORABILITY\",\n        \"COMPETITOR1_ACCESS_FAVORABILITY\",\n        \"COMPETITOR2_ACCESS_FAVORABILITY\",\n        \"COMPETITOR3_ACCESS_FAVORABILITY\",\n        \"FAST_ACCESS_SCORE_BUCKET\",\n        \"HCP_PAYER_FAST_ACCESS_SCORE\",\n        \"HCP_FAST_ACCESS_SCORE\",\n        \"PAYER_FAST_ACCESS_SCORE\",\n        \"STATE_FAST_ACCESS_SCORE\",\n        \"TRADITIONAL_SCORE\",\n        CASE\n            WHEN \"PERIOD\" ~ '^[0-9]{6}$' THEN to_date(\"PERIOD\",'YYYYMM')\n            WHEN \"PERIOD\" ~ '^[0-9]{4}-[0-9]{2}-[0-9]{2}$' THEN to_date(\"PERIOD\",'YYYY-MM-DD')\n            ELSE NULL\n        END AS period_date\n    FROM \"fast\".\"Updated_FAST_Table_MVP_Unpivot\"\n    WHERE \"METRIC\" = 'TRX'\n),\n\nLATEST_PERIOD_CTE AS (\n    SELECT MAX(period_date) AS latest_period\n    FROM period_cast\n),\n\nHCP_FAST_SCORES AS (\n    SELECT\n        u.\"HCP_ID\",\n        u.\"BENCHMARK_FAST_SCORE\",\n        AVG(u.\"TRADITIONAL_SCORE\") AS benchmark_traditional_fast_score,\n\n        SUM(\n            CASE WHEN u.period_date = l.latest_period\n                 THEN u.\"VOLUME\" * u.\"FAST_ACCESS_SCORE\"\n                 ELSE 0\n            END\n        ) / NULLIF(SUM(u.\"VOLUME\"),0) AS fast_access_score,\n\n        SUM(\n            CASE WHEN u.period_date = l.latest_period\n                 THEN u.\"VOLUME\" * u.\"TRADITIONAL_SCORE\"\n                 ELSE 0\n            END\n        ) / NULLIF(SUM(u.\"VOLUME\"),0) AS traditional_access_score,\n\n        SUM(CASE WHEN UPPER(u.\"PRODUCT\")='CARDIZOR'\n                 THEN u.\"VOLUME\" ELSE 0 END)\n        / NULLIF(SUM(u.\"VOLUME\"),0) AS market_share\n\n    FROM period_cast u\n    CROSS JOIN LATEST_PERIOD_CTE l\n\n    WHERE u.period_date &gt;= l.latest_period - INTERVAL '12 months'\n\n    GROUP BY u.\"HCP_ID\", u.\"BENCHMARK_FAST_SCORE\"\n\n    HAVING SUM(CASE WHEN UPPER(u.\"PRODUCT\")='CARDIZOR' THEN 1 ELSE 0 END) &gt; 0\n),\n\nSCALED_HCP_SCORES AS (\n    SELECT\n        \"HCP_ID\",\n        fast_access_score,\n        traditional_access_score,\n        \"BENCHMARK_FAST_SCORE\",\n        benchmark_traditional_fast_score,\n        market_share,\n\n        CASE\n            WHEN fast_access_score IS NULL\n                 OR NULLIF(MAX(fast_access_score) OVER()\n                            - MIN(fast_access_score) OVER(),0) IS NULL\n            THEN NULL\n            ELSE (fast_access_score - MIN(fast_access_score) OVER())\n                / (MAX(fast_access_score) OVER() - MIN(fast_access_score) OVER())\n        END AS scaled_fast_access_score,\n\n        CASE\n            WHEN traditional_access_score IS NULL\n                 OR NULLIF(MAX(traditional_access_score) OVER()\n                            - MIN(traditional_access_score) OVER(),0) IS NULL\n            THEN NULL\n            ELSE (traditional_access_score - MIN(traditional_access_score) OVER())\n                / (MAX(traditional_access_score) OVER() - MIN(traditional_access_score) OVER())\n        END AS scaled_traditional_access_score\n\n    FROM HCP_FAST_SCORES\n),\n\nSCORED_HCP_CATEGORIES AS (\n    SELECT\n        \"HCP_ID\",\n        scaled_fast_access_score,\n        scaled_traditional_access_score,\n        \"BENCHMARK_FAST_SCORE\",\n        benchmark_traditional_fast_score,\n        market_share\n    FROM SCALED_HCP_SCORES\n)\n\nSELECT\n    \"HCP_ID\",\n    \"BENCHMARK_FAST_SCORE\",\n    market_share AS CardizorMarketShare,\n    scaled_fast_access_score AS ScaledFastAccessScore,\n    scaled_traditional_access_score AS ScaledTraditionalAccessScore,\n    CASE\n        WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n         AND scaled_fast_access_score &gt; \"BENCHMARK_FAST_SCORE\"\n        THEN 'True Positive (Traditional)'\n        WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n         AND scaled_fast_access_score &lt; \"BENCHMARK_FAST_SCORE\"\n        THEN 'False Positive (Traditional)'\n        ELSE NULL\n    END AS performance_category\n\nFROM SCORED_HCP_CATEGORIES\n\nWHERE (\n        CASE\n            WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n             AND scaled_fast_access_score &gt; \"BENCHMARK_FAST_SCORE\"\n            THEN 'True Positive (Traditional)'\n            WHEN scaled_traditional_access_score &gt; benchmark_traditional_fast_score\n             AND scaled_fast_access_score &lt; \"BENCHMARK_FAST_SCORE\"\n            THEN 'False Positive (Traditional)'\n            ELSE NULL\n        END\n    ) IS NOT NULL\n\nORDER BY scaled_fast_access_score DESC;",
+            "sql_result": {
+                "datasets": [
+                    {
+                        "label": "False Positive (Traditional)",
+                        "data": [
+                            {
+                                "x": 0,
+                                "y": 0.3874946440616334,
+                                "label": "18649543",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3935300471138515,
+                                "label": "6068217",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3915677510645455,
+                                "label": "25274950",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3914179863394806,
+                                "label": "5295748",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3893263407054183,
+                                "label": "10446538",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4025505204461489,
+                                "label": "4192409",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4019657649107294,
+                                "label": "3704415",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4017239993460303,
+                                "label": "5095785",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4082877163462044,
+                                "label": "5105268",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3842515018029714,
+                                "label": "5915529",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3842156366418556,
+                                "label": "30783585",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3125543801914136,
+                                "label": "22480976",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3259477346591404,
+                                "label": "35632174",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3258144357642281,
+                                "label": "7565912",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3232225022233223,
+                                "label": "5881491",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3188560435439515,
+                                "label": "6651599",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3173561188048308,
+                                "label": "12048657",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3541804187250981,
+                                "label": "19094039",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.339631682968026,
+                                "label": "51379424",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.304129220229656,
+                                "label": "6960359",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3088219184676404,
+                                "label": "4164810",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3339982205228334,
+                                "label": "53039620",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.2401264254135473,
+                                "label": "4503189",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3305058447742187,
+                                "label": "5292523",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3290235469634846,
+                                "label": "6726003",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3278500197829481,
+                                "label": "31464258",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3570227574353444,
+                                "label": "5531065",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.355622692772102,
+                                "label": "21744867",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3551975194353741,
+                                "label": "18639675",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4218726491362665,
+                                "label": "25133384",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3763773031701457,
+                                "label": "14498627",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.373932674330407,
+                                "label": "5276650",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3733232861279524,
+                                "label": "4204481",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3508618689311831,
+                                "label": "6099963",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3319860810385752,
+                                "label": "10555664",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3672761869425729,
+                                "label": "29550857",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4193764676047008,
+                                "label": "5365433",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4191454092576291,
+                                "label": "21211686",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4175708556941284,
+                                "label": "11200242",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4174156640824562,
+                                "label": "36683939",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4164620224574064,
+                                "label": "16446680",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3721038034708753,
+                                "label": "5558018",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3705974206423312,
+                                "label": "15645592",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.3704080444471938,
+                                "label": "30776906",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4116921747376069,
+                                "label": "3524687",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4205587642498535,
+                                "label": "22449641",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0,
+                                "y": 0.4204414884220036,
+                                "label": "5502540",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.004582774455002714,
+                                "y": 0.3558601415685602,
+                                "label": "19675949",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.0046576988835141655,
+                                "y": 0.3688230571664206,
+                                "label": "36546418",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.005837857771131241,
+                                "y": 0.3680883111437548,
+                                "label": "6102534",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.0062709444344555935,
+                                "y": 0.3805927295303305,
+                                "label": "5196023",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.007401824859096735,
+                                "y": 0.3010710171047162,
+                                "label": "21008142",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.008084066354762056,
+                                "y": 0.3320686542818434,
+                                "label": "21022057",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.008881894604053454,
+                                "y": 0.3902520009569326,
+                                "label": "19109317",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.008968291752521245,
+                                "y": 0.3947005446878356,
+                                "label": "36704585",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.009185977522742859,
+                                "y": 0.2761697379823667,
+                                "label": "5867307",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.01198077911888755,
+                                "y": 0.410963032837742,
+                                "label": "4210101",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.013259668449681024,
+                                "y": 0.3535216710107509,
+                                "label": "11652342",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.01369138373770162,
+                                "y": 0.3396532328920984,
+                                "label": "5773469",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.01380362021588821,
+                                "y": 0.3791109741281477,
+                                "label": "36225737",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.01470202134268915,
+                                "y": 0.3471037993287987,
+                                "label": "4327705",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.015335984658038046,
+                                "y": 0.3552242930684143,
+                                "label": "36510261",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.015469690942815542,
+                                "y": 0.3914587115115856,
+                                "label": "7758079",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.016293905918419622,
+                                "y": 0.2995747892453196,
+                                "label": "36701578",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.02120725038523451,
+                                "y": 0.4148970781644029,
+                                "label": "5476675",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.02366244896784663,
+                                "y": 0.366271235342624,
+                                "label": "24645458",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.024152763183889942,
+                                "y": 0.3652129074449832,
+                                "label": "5992603",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.0243288484578676,
+                                "y": 0.2824266981329426,
+                                "label": "30819826",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.026102005593288055,
+                                "y": 0.4158716685673361,
+                                "label": "21388776",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.026143790849673203,
+                                "y": 0.3813313743015811,
+                                "label": "19517810",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.026296893565883377,
+                                "y": 0.2631735228501205,
+                                "label": "27290224",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.027522935779816515,
+                                "y": 0.4011575373663379,
+                                "label": "5502837",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.029289775766301245,
+                                "y": 0.3629546263628366,
+                                "label": "17637050",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.02972865768219462,
+                                "y": 0.4111477468213231,
+                                "label": "4232085",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.029888642952339683,
+                                "y": 0.2667912174486982,
+                                "label": "4542753",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.030687135535582517,
+                                "y": 0.2985331227811728,
+                                "label": "4449247",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03136678336105225,
+                                "y": 0.3869786789357152,
+                                "label": "21155831",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.0345051026437382,
+                                "y": 0.3144732216484961,
+                                "label": "36594149",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03557661393522737,
+                                "y": 0.3608480150871822,
+                                "label": "6790997",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.036036834530030024,
+                                "y": 0.292709245981445,
+                                "label": "8292486",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03650297842098907,
+                                "y": 0.3806356466732214,
+                                "label": "6153731",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03677542234209638,
+                                "y": 0.4060404666087371,
+                                "label": "39518335",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03744849133515562,
+                                "y": 0.3762530105162919,
+                                "label": "6929326",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03785520478667046,
+                                "y": 0.2703158592770471,
+                                "label": "19260606",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.038710240915647176,
+                                "y": 0.411569385092177,
+                                "label": "36703130",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.03944254556635575,
+                                "y": 0.2912098678588501,
+                                "label": "4670935",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.040021011991799985,
+                                "y": 0.2237108317020096,
+                                "label": "18348520",
+                                "category": "False Positive (Traditional)"
+                            },
+                            {
+                                "x": 0.040931174632194166,
+                         </t>
+  </si>
+  <si>
+    <t>benchmark_cluster</t>
   </si>
 </sst>
 </file>
@@ -6373,7 +6373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E902A12F-1E09-4ECD-9E58-CDE88C9042AC}">
   <dimension ref="A1:D190"/>
-  <sheetFormatPr defaultRowHeight="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.77734375" customWidth="1"/>
     <col min="2" max="2" width="68.5546875" customWidth="1"/>
@@ -6381,750 +6381,750 @@
     <col min="4" max="4" width="37.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="8" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="C7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="D7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D8" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="D9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>38</v>
+      <c r="D11" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="12" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="D14" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="7" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
     </row>
-    <row r="34" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
     </row>
-    <row r="51" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
     </row>
-    <row r="52" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
     </row>
-    <row r="53" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
     </row>
-    <row r="54" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
     </row>
-    <row r="55" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
     </row>
-    <row r="56" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
     </row>
-    <row r="57" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
     </row>
-    <row r="58" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
     </row>
-    <row r="59" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
     </row>
-    <row r="60" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
     </row>
-    <row r="61" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
     </row>
-    <row r="62" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
     </row>
-    <row r="63" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
     </row>
-    <row r="64" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
     </row>
-    <row r="65" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
     </row>
-    <row r="66" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
     </row>
-    <row r="67" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
     </row>
-    <row r="68" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
     </row>
-    <row r="69" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
     </row>
-    <row r="70" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
     </row>
-    <row r="71" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
     </row>
-    <row r="72" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
     </row>
-    <row r="105" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
     </row>
-    <row r="106" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
     </row>
-    <row r="107" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
     </row>
-    <row r="108" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
     </row>
-    <row r="109" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
     </row>
-    <row r="110" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
     </row>
-    <row r="112" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
     </row>
-    <row r="113" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
     </row>
-    <row r="114" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
     </row>
-    <row r="115" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
     </row>
-    <row r="117" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
     </row>
-    <row r="124" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
     </row>
-    <row r="125" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
     </row>
-    <row r="145" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
     </row>
-    <row r="146" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
     </row>
-    <row r="161" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
     </row>
-    <row r="162" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
     </row>
-    <row r="177" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
     </row>
-    <row r="178" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
     </row>
-    <row r="180" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
     </row>
-    <row r="181" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
     </row>
-    <row r="182" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
     </row>
-    <row r="183" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
     </row>
-    <row r="184" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
     </row>
-    <row r="185" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
     </row>
-    <row r="186" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
     </row>
-    <row r="187" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
     </row>
-    <row r="188" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
     </row>
-    <row r="189" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
     </row>
-    <row r="190" spans="1:1" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
     </row>
   </sheetData>
